--- a/IT23653986 - Assignment 1 - Test cases.xlsx
+++ b/IT23653986 - Assignment 1 - Test cases.xlsx
@@ -490,7 +490,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F201"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="1" max="1"/>
     <col width="22.109375" customWidth="1" min="3" max="3"/>
@@ -3336,8 +3336,8 @@
   </sheetData>
   <mergeCells count="300">
     <mergeCell ref="C14:C17"/>
+    <mergeCell ref="B66:B69"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="B66:B69"/>
     <mergeCell ref="C154:C157"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="A166:A169"/>

--- a/IT23653986 - Assignment 1 - Test cases.xlsx
+++ b/IT23653986 - Assignment 1 - Test cases.xlsx
@@ -129,19 +129,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -490,7 +490,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F201"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1" outlineLevelCol="0"/>
   <cols>
     <col width="10.88671875" customWidth="1" min="1" max="1"/>
     <col width="22.109375" customWidth="1" min="3" max="3"/>
@@ -534,32 +534,32 @@
       </c>
     </row>
     <row r="2" ht="49.95" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Neg_0001</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">M </t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>mtRs2500konline transferkrnna puluwnd</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>මට Rs.2500ක් online transfer කරන්න පුළුවන්ද?</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>මට RRs2500konline transfer කරන්න පුළුවන්ද</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -590,22 +590,22 @@
       <c r="F5" s="4" t="n"/>
     </row>
     <row r="6" ht="49.95" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Neg_0002</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>kasunaiye meetingeknpsse callkrnn</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>කසුන් අයියේ meeting එකෙන් පස්සේ call කරන්න</t>
         </is>
@@ -615,7 +615,7 @@
           <t>කසුනයිඅයේ meeting එකෙන් පස්සේ call කරන්න</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -646,32 +646,32 @@
       <c r="F9" s="4" t="n"/>
     </row>
     <row r="10" ht="49.95" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Neg_0003</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>mekauploadkrddi error ekak awabn!!!</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>මේක upload කරද්දී error එකක් ආවා බන්!!!</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>මේකupload කරද්දී error එකක් අවබන්!!!</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -702,22 +702,22 @@
       <c r="F13" s="4" t="n"/>
     </row>
     <row r="14" ht="49.95" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Neg_0004</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>apiGallewalin2ktapitatwenwa😅</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>අපි Galle වලින් 2ට පිටත් වෙනවා 😅</t>
         </is>
@@ -727,7 +727,7 @@
           <t>අපි ගල්ලෙවලින්2ක්ටපටිට්වෙනවා😅</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -758,32 +758,32 @@
       <c r="F17" s="4" t="n"/>
     </row>
     <row r="18" ht="49.95" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Neg_0005</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>adalectureekalabekedahallekeda?</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>අද lecture එක lab එකේද hall එකේද?</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>අදාලීකාලබේකෑඩහලේකෑඩ?</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -814,22 +814,22 @@
       <c r="F21" s="4" t="n"/>
     </row>
     <row r="22" ht="49.95" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Neg_0006</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>mnhithuweoyaennakiyalane</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>මං හිතුවේ ඔයා එන්න කියලා නේ</t>
         </is>
@@ -839,7 +839,7 @@
           <t>ම්න්හිතුවේඔයඑන්නකියලානේ</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -870,32 +870,32 @@
       <c r="F25" s="4" t="n"/>
     </row>
     <row r="26" ht="49.95" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Neg_0007</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>eka2026-05-01taschedulekrnn</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>ඒක 2026-05-01ට schedule කරන්න</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>එක 2026-05-01ටච්චේදුලේකරන්න</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -926,22 +926,22 @@
       <c r="F29" s="4" t="n"/>
     </row>
     <row r="30" ht="49.95" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Neg_0008</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>mnzoom join krnnan bn</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>මං Zoom join කරන්නන් බන්</t>
         </is>
@@ -951,7 +951,7 @@
           <t>mnzoom join කරන්නන් බන්</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -982,32 +982,32 @@
       <c r="F33" s="4" t="n"/>
     </row>
     <row r="34" ht="49.95" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Neg_0009</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>mtotp eka labuna</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>මට OTP එක ලැබුණා</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>මටොට්ප් එක ලැබුණා</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1038,22 +1038,22 @@
       <c r="F37" s="4" t="n"/>
     </row>
     <row r="38" ht="49.95" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Neg_0010</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>mnerror ekak dekka bn</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>මං error එකක් දැක්කා බන්</t>
         </is>
@@ -1063,7 +1063,7 @@
           <t>mnerror එකක් දැක්කා බන්</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1094,32 +1094,32 @@
       <c r="F41" s="4" t="n"/>
     </row>
     <row r="42" ht="49.95" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Neg_0011</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>oytapp eka wada ndda</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>ඔයාට app එක වැඩ නැද්ද</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>ඔයාටpp එක වැඩ නැද්ද</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1150,22 +1150,22 @@
       <c r="F45" s="4" t="n"/>
     </row>
     <row r="46" ht="49.95" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Neg_0012</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>mtupload krnn bari ai</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>මට upload කරන්න බැරි ඇයි</t>
         </is>
@@ -1175,7 +1175,7 @@
           <t>මටupload කරන්න බැරි ඇයි</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1206,32 +1206,32 @@
       <c r="F49" s="4" t="n"/>
     </row>
     <row r="50" ht="49.95" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Neg_0013</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>meebrowser 1ka slow da bn</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>මේ browser එක slow ද බන්</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>මීබ්රොසෙර් එක slow ද බන්</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1262,22 +1262,22 @@
       <c r="F53" s="4" t="n"/>
     </row>
     <row r="54" ht="49.95" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Neg_0014</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>oytfile eka ganna puluwnd</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>ඔයාට file එක ගන්න පුළුවන්ද</t>
         </is>
@@ -1287,7 +1287,7 @@
           <t>ඔයාට ෆයිල් එක ගන්න පුළුවන්ද</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1318,32 +1318,32 @@
       <c r="F57" s="4" t="n"/>
     </row>
     <row r="58" ht="49.95" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Neg_0015</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>mtvideos play wenne naha</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>මට videos play වෙන්නේ නැහැ</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>mtvideos play වෙන්නේ නැහැ</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1374,22 +1374,22 @@
       <c r="F61" s="4" t="n"/>
     </row>
     <row r="62" ht="49.95" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Neg_0016</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
         <is>
           <t>oytmypasswrd eka resetkrnn plz</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>ඔයාට මගේ password එක reset කරන්න please</t>
         </is>
@@ -1399,7 +1399,7 @@
           <t>ඔයාට mypass වැරැද්ද ඒක reset කරන්න please</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1430,32 +1430,32 @@
       <c r="F65" s="4" t="n"/>
     </row>
     <row r="66" ht="49.95" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Neg_0017</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>apiColombowalin3ta pitathwenwa😅</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>අපි Colombo වලින් 3ට පිටත් වෙනවා 😅</t>
         </is>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>අපි කොලොම්බොවලින් පිටත්වෙනවා😅</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1486,22 +1486,22 @@
       <c r="F69" s="4" t="n"/>
     </row>
     <row r="70" ht="49.95" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Neg_0018</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">mnhitnna epa oy meka dnnw kiyala </t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
         <is>
           <t>මං හිතන්න එපා ඔයා මේක දන්නවා කියලා</t>
         </is>
@@ -1511,7 +1511,7 @@
           <t>මන්හිට්න්න එපා ඔයා මේක දන්නවා කියලා</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1542,32 +1542,32 @@
       <c r="F73" s="4" t="n"/>
     </row>
     <row r="74" ht="49.95" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>Neg_0019</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>mtaZoomlink eka ewnnm puluwnd</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>මට Zoom link එක එවන්නම් පුළුවන්ද</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>මට Zoomlink එක එවන්නම් පුළුවන්ද</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1598,22 +1598,22 @@
       <c r="F77" s="4" t="n"/>
     </row>
     <row r="78" ht="49.95" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Neg_0020</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>oymail eka baluwed chenuka@test.com</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
         <is>
           <t>ඔයා mail එක බැලුවද chenuka@test.com</t>
         </is>
@@ -1623,7 +1623,7 @@
           <t>ඔයාමයිල් එක බැලුවෙද chenuka@test.com</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1654,32 +1654,32 @@
       <c r="F81" s="4" t="n"/>
     </row>
     <row r="82" ht="49.95" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>Neg_0021</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>apitrip eka cancel krnna wenwada bn</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr">
         <is>
           <t>අපි trip එක cancel කරන්න වෙනවද බන්</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>අපිටrip එක cancel කරන්න වෙනවද බන්</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1710,22 +1710,22 @@
       <c r="F85" s="4" t="n"/>
     </row>
     <row r="86" ht="49.95" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Neg_0022</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>mtRs7500kthibba eth iwrai bn</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>මට Rs.7500ක් තිබ්බා එත් ඉවරයි බන්</t>
         </is>
@@ -1735,7 +1735,7 @@
           <t>මට RRs7500කටයිබ ඒත් ඉවරයි බන්</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1766,32 +1766,32 @@
       <c r="F89" s="4" t="n"/>
     </row>
     <row r="90" ht="49.95" customHeight="1">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>Neg_0023</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>oyatekka meeting ekk hadnn puluwnd</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>ඔයාට එක්ක meeting එකක් හදන්න පුළුවන්ද</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>ඔයාට දැක්ක meeting එකක් හදන්න පුළුවන්ද</t>
         </is>
       </c>
-      <c r="F90" s="7" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1822,22 +1822,22 @@
       <c r="F93" s="4" t="n"/>
     </row>
     <row r="94" ht="49.95" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>Neg_0024</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>mnlogin wenna giyama error ekk awa</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>මං login වෙන්න ගියම error එකක් ආවා</t>
         </is>
@@ -1847,7 +1847,7 @@
           <t>මන් ලොගින් වෙන්න ගියාම error එකක් ආවා</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1878,32 +1878,32 @@
       <c r="F97" s="4" t="n"/>
     </row>
     <row r="98" ht="49.95" customHeight="1">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>Neg_0025</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>apimeweekend party ekk danaw bn</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D98" s="7" t="inlineStr">
         <is>
           <t>අපි මේ weekend party එකක් දානවා බන්</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>අපිමේවීකෙන්ඩ් party එකක් දානවා බන්</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1934,22 +1934,22 @@
       <c r="F101" s="4" t="n"/>
     </row>
     <row r="102" ht="49.95" customHeight="1">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>Neg_0026</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>oyameka balala kiyanna puluwnd meka correct translate wenwada ndda bn</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>ඔයා මේක බලලා කියන්න පුළුවන්ද මේක correct translate වෙනවද නැද්ද බන්</t>
         </is>
@@ -1959,7 +1959,7 @@
           <t>ඔයාමේක බලලා කියන්න පුළුවන්ද මේක correct translate වෙනවද නැද්ද බං</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -1990,32 +1990,32 @@
       <c r="F105" s="4" t="n"/>
     </row>
     <row r="106" ht="49.95" customHeight="1">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>Neg_0027</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C106" s="5" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>mnkalin use karapu app ekata wada meka poddk slow wage penenwa bn</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>මං කලින් use කරපු app එකට වඩා මේක පොඩ්ඩක් slow වගේ පේනවා බන්</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>මන්කලින් use කරපු app එකට වඩා මේක පොඩ්ඩක් slow වගේ පෙනෙනවා බං</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2046,22 +2046,22 @@
       <c r="F109" s="4" t="n"/>
     </row>
     <row r="110" ht="49.95" customHeight="1">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>Neg_0028</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>mnhithnne me translator eka slang words tika hariyata handle krnne ne bn</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>මං හිතන්නේ මේ translator එක slang words ටික හරියට handle කරන්නේ නෑ බන්</t>
         </is>
@@ -2071,7 +2071,7 @@
           <t>මන් හිතාන්නේ මේ translator එක slang words ටික හරියට handle කරන්නේ නෑ බං</t>
         </is>
       </c>
-      <c r="F110" s="7" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2102,32 +2102,32 @@
       <c r="F113" s="4" t="n"/>
     </row>
     <row r="114" ht="49.95" customHeight="1">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>Neg_0029</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>apinextmonth project deadline ekata kalin okkoma tasks finish krnn ona bn</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>අපි next month project deadline එකට කලින් ඔක්කොම tasks finish කරන්න ඕන බන්</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>අපිනෙක්ස්ට්මොන්ත් project deadline එකට කලින් ඔක්කොම tasks finish කරන්න ඕන බං</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2158,22 +2158,22 @@
       <c r="F117" s="4" t="n"/>
     </row>
     <row r="118" ht="49.95" customHeight="1">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>Neg_0030</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>oytype krna widiyata poddk change kaloth better result enwa kiyala hithenwa</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D118" s="7" t="inlineStr">
         <is>
           <t>ඔයා type කරන විදිහට පොඩ්ඩක් change කලොත් better result එනවා කියලා හිතෙනවා</t>
         </is>
@@ -2183,7 +2183,7 @@
           <t>ඔයිට්පේ කරන විදියට පොඩ්ඩක් change කලොත් බෙලිර් result එනවා කියලා හිතෙනවා</t>
         </is>
       </c>
-      <c r="F118" s="7" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2214,32 +2214,32 @@
       <c r="F121" s="4" t="n"/>
     </row>
     <row r="122" ht="49.95" customHeight="1">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>Neg_0031</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="C122" s="6" t="inlineStr">
         <is>
           <t>mt me system eka use krddi godak errors dekka nisa ewa list krnn ona bn</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
         <is>
           <t>මට මේ system එක use කරද්දී ගොඩක් errors දැක්කා නිසා ඒවා list කරන්න ඕන බන්</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>මට මේ system එක use කරද්දී ගොඩක් errors දැක්ක නිසා ඒවා list කරන්න ඕන බන්</t>
         </is>
       </c>
-      <c r="F122" s="7" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2270,22 +2270,22 @@
       <c r="F125" s="4" t="n"/>
     </row>
     <row r="126" ht="49.95" customHeight="1">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>Neg_0032</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C126" s="5" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>oyainput eka change karala try karanna puluwnd eken output eka wenas wenwada balanna</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr">
         <is>
           <t>ඔයා input එක change කරලා try කරන්න පුළුවන්ද ඒකෙන් output එක වෙනස් වෙනවද බලන්න</t>
         </is>
@@ -2295,7 +2295,7 @@
           <t>ඔයinput එක change කරලා try කරන්න පුළුවන්ද ඒකෙන් output එක වෙනස් වෙනවාද බලන්න</t>
         </is>
       </c>
-      <c r="F126" s="7" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2326,32 +2326,32 @@
       <c r="F129" s="4" t="n"/>
     </row>
     <row r="130" ht="49.95" customHeight="1">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>Neg_0033</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>machan mn heta ude 8.15AMta online class ekata joinwenna hithan inne eth WiFi password eka wenaswela nisa Teams link ekath openwenne nane. oyata puluwannam password eka resetkarala new link eka WhatsApp walin ewanna. mama 9.00AMta presentation ekata ready wenna one nisa poddak ikmanata balanna bn please meka ikmanata balanna</t>
         </is>
       </c>
-      <c r="D130" s="6" t="inlineStr">
+      <c r="D130" s="7" t="inlineStr">
         <is>
           <t>මචං මං හෙට උදේ 8.15AMට online class එකට join වෙන්න හිතන් ඉන්නේ එත් WiFi password එක වෙනස් වෙලා නිසා Teams link එකත් open වෙන්නේ නෑනේ. ඔයාට පුළුවන්නම් password එක reset කරලා new link එක WhatsApp වලින් එවන්න. මම 9.00AMට presentation එකට ready වෙන්න ඕන නිසා පොඩ්ඩක් ඉක්මනට බලන්න බන් please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E130" s="7" t="inlineStr">
         <is>
           <t>මචන් මන් හෙට උදේ 8.15AMට online class එකට join වෙන්න හිතන් ඉන්නේ ඒත් WiFi password එක වෙනස්වෙලා නිසා Teams link එකත් open වෙන්නේ නෑනේ. ඔයාට පුලුවන්නම් password එක resetකරලා new link එක WhatsApp වලින් එවන්න. මම 9.00AMට presentation එකට ready වෙන්න ඕනේ නිසා පොඩ්ඩක් ඉක්මනට බලන්න බන් please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="F130" s="7" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2382,22 +2382,22 @@
       <c r="F133" s="4" t="n"/>
     </row>
     <row r="134" ht="49.95" customHeight="1">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>Neg_0034</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>ape group eke ayata mama GitHubrepo link eka emailkala eth kasun kiyanawa ZIPfile eka downloadkaraddi error ekak enawa kiyala. eya 2026-05-04ta submission karanna hithan inne nisa mata screenshot ekak ewanna kiwwa. oyata puluwannam GoogleDrive link ekak widihata sharekaranna machan please meka ikmanata balanna</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
+      <c r="D134" s="7" t="inlineStr">
         <is>
           <t>අපේ group එකේ අයට මම GitHub repo link එක email කළා එත් කසුන් කියනවා ZIP file එක download කරද්දී error එකක් එනවා කියලා. එයා 2026-05-04ට submission කරන්න හිතන් ඉන්නේ නිසා මට screenshot එකක් එවන්න කිව්වා. ඔයාට පුළුවන්නම් Google Drive link එකක් විදිහට share කරන්න මචං please මේක ඉක්මනට බලන්න</t>
         </is>
@@ -2407,7 +2407,7 @@
           <t>අපේ group එකේ අයට මම GitHubrepo link එක email කළා ඒත් කසුන් කියනවා ZIPfile එක download කරද්දි error එකක් එනවා කියලා. එය 2026-05-04ට submission කරන්න හිතන් ඉන්නේ නිසා මට screenshot එකක් එවන්න කිව්වා. ඔයාට පුලුවන්නම් GoogleDrive link එකක් විදිහට ශරීකරන්න මචන් please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="F134" s="7" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2438,32 +2438,32 @@
       <c r="F137" s="4" t="n"/>
     </row>
     <row r="138" ht="49.95" customHeight="1">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>Neg_0035</t>
         </is>
       </c>
-      <c r="B138" s="7" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C138" s="5" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>sirawata uba e invoice eke Rs24500k kiyala dakkada nadda mata nam amount eka wrong wage penawa. mama onlinepay karaddi receipt eka email ekata awe nane. oyata puluwannam bank message eka checkkarala screenshot ekak ewanna. meka 5.30pmta kalin confirmkaranna one bn please meka ikmanata balanna ada submit krnna one</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
+      <c r="D138" s="7" t="inlineStr">
         <is>
           <t>සිරාවට උඹ ඒ invoice එකේ Rs.24500ක් කියලා දැක්කද නැද්ද මට නම් amount එක wrong වගේ පේනවා. මම online pay කරද්දී receipt එක email එකට ආවේ නෑනේ. ඔයාට පුළුවන්නම් bank message එක check කරලා screenshot එකක් එවන්න. මේක 5.30pmට කලින් confirm කරන්න ඕන බන් please මේක ඉක්මනට බලන්න අද submit කරන්න ඕන</t>
         </is>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="7" t="inlineStr">
         <is>
           <t>සිරාවට උඹ ඒ invoice එකේ Rs24500ක් කියලා දැක්කද නැද්ද මට නම් amount එක wrong වගේ පේනවා. මම onlinepay කරද්දි receipt එක email එකට ආවේ නෑනේ. ඔයාට පුලුවන්නම් bank message එක check කරලා screenshot එකක් එවන්න. මේක 5.30pmට කලින් confirm කරන්න ඕනේ බන් please මේක ඉක්මනට බලන්න අද submit කරන්න ඕනේ</t>
         </is>
       </c>
-      <c r="F138" s="7" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2494,22 +2494,22 @@
       <c r="F141" s="4" t="n"/>
     </row>
     <row r="142" ht="49.95" customHeight="1">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>Neg_0036</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C142" s="5" t="inlineStr">
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>mama ColomboFort walin 5.30pmta bus ekata naginna hithuwe eth GoogleMap eke traffic eka red wela pennanawa bn. api Negombo walata 7PMta yanna plan kala nisa oyatath enna puluwannam location link eka sharekaranna. bus number eka 240da 187da kiyala mata hariyata mathaka ne please meka ikmanata balanna</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
+      <c r="D142" s="7" t="inlineStr">
         <is>
           <t>මම Colombo Fort වලින් 5.30pmට bus එකට නැගින්න හිතුවේ එත් Google Map එකේ traffic එක red වෙලා පෙන්වනවා බන්. අපි Negombo වලට 7PMට යන්න plan කළා නිසා ඔයාටත් එන්න පුළුවන්නම් location link එක share කරන්න. bus number එක 240ද 187ද කියලා මට හරියට මතක නෑ please මේක ඉක්මනට බලන්න</t>
         </is>
@@ -2519,7 +2519,7 @@
           <t>මම ColomboFort වලින් 5.30pmට bus එකට නගින්න හිතුවේ ඒත් GoogleMap එකේ traffic එක red වෙලා පෙන්නනවා බන්. අපි Negombo වලට 7PMට යන්න plan කළා නිසා ඔයාටත් එන්න පුලුවන්නම් location link එක sharek කරන්න. bus number එක 240ද 187ද කියලා මට හරියට මතක නෑ please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="F142" s="7" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2550,32 +2550,32 @@
       <c r="F145" s="4" t="n"/>
     </row>
     <row r="146" ht="49.95" customHeight="1">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" s="5" t="inlineStr">
         <is>
           <t>Neg_0037</t>
         </is>
       </c>
-      <c r="B146" s="7" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C146" s="5" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>oya mage new password eka resetkarala OTP eka labunama WhatsApp message ekak danna mokada mama dan call ekaka inne. login page eke error500 kiyala pennanawa nisa browser cache clear karala baluwath hari giye ne. mage email eka chenuka2026@test.com kiyala enterkaranna amathaka karanna epa please meka ikmanata balanna</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D146" s="7" t="inlineStr">
         <is>
           <t>ඔයා මගේ new password එක reset කරලා OTP එක ලැබුණම WhatsApp message එකක් දාන්න මොකද මම දැන් call එකක ඉන්නේ. login page එකේ error 500 කියලා පෙන්වනවා නිසා browser cache clear කරලා බැලුවත් හරි ගියේ නෑ. මගේ email එක chenuka2026@test.com කියලා enter කරන්න අමතක කරන්න එපා please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="7" t="inlineStr">
         <is>
           <t>ඔයා මගේ new password එක reset කරලා OTP ඒක ලැබුණාම WhatsApp message එකක් දාන්න මොකද මම දැන් call එකක ඉන්නේ. login page එකේ error500 කියලා පෙන්නනවා නිසා browser cache clear කරලා බැලුවත් හරි ගියේ නෑ. මගේ email එක chenuka2026@test.com කියලා ඇන්ටෙර්කරන්න අමතක කරන්න එපා please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="F146" s="7" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2606,22 +2606,22 @@
       <c r="F149" s="4" t="n"/>
     </row>
     <row r="150" ht="49.95" customHeight="1">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>Neg_0038</t>
         </is>
       </c>
-      <c r="B150" s="7" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C150" s="5" t="inlineStr">
+      <c r="C150" s="6" t="inlineStr">
         <is>
           <t>api next Friday 2026-05-08ta lab test ekak thiyenawa kiyala lecturer Teamschat eke dala thibba eka oyala dakkada? mata time eka 2.30PMda 3PMda kiyala sure ne. oyata screenshot ekak thiyenawanam group ekata danna. exam hall eka labA da labB da kiyala thama confirm wela nadda bn please meka ikmanata balanna</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
+      <c r="D150" s="7" t="inlineStr">
         <is>
           <t>අපි next Friday 2026-05-08ට lab test එකක් තියෙනවා කියලා lecturer Teams chat එකේ දාලා තිබ්බා ඒක ඔයාලා දැක්කද? මට time එක 2.30PMද 3PMද කියලා sure නෑ. ඔයාට screenshot එකක් තියෙනවනම් group එකට දාන්න. exam hall එක lab A ද lab B ද කියලා තාම confirm වෙලා නැද්ද බන් please මේක ඉක්මනට බලන්න</t>
         </is>
@@ -2631,7 +2631,7 @@
           <t>අපි next Friday 2026-05-08ට lab test එකක් තියෙනවා කියලා lecturer Teamschat එකේ දාලා තිබ්බ එක ඔයාලා දැක්කද? මට ටයිම් එක 2.30PMද 3PMද කියලා sure නේ. ඔයාට screenshot එකක් තියෙනවානම් group එකට දාන්න. exam hall එක ලාබ ද ලබ්බ ද කියලා තාම confirm වෙලා නැද්ද බන් please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="F150" s="7" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2662,32 +2662,32 @@
       <c r="F153" s="4" t="n"/>
     </row>
     <row r="154" ht="49.95" customHeight="1">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>Neg_0039</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C154" s="5" t="inlineStr">
+      <c r="C154" s="6" t="inlineStr">
         <is>
           <t>mata PDF file eka 25MBta wada loku nisa uploadwenne nane ithin link ekak widihata GoogleDrive eke sharekaranna hithan inne. oyata puluwannam file name eka IT3040_Assignment1_Final.pdf kiyala renamekarala permission anyone-with-link walata setkaranna. nathnam lecturer openkaraddi access issue enawa please meka ikmanata balanna</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
+      <c r="D154" s="7" t="inlineStr">
         <is>
           <t>මට PDF file එක 25MBට වඩා ලොකු නිසා upload වෙන්නේ නෑනේ ඉතින් link එකක් විදිහට Google Drive එකේ share කරන්න හිතන් ඉන්නේ. ඔයාට පුළුවන්නම් file name එක IT3040_Assignment1_Final.pdf කියලා rename කරලා permission anyone-with-link වලට set කරන්න. නැත්නම් lecturer open කරද්දී access issue එනවා please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="7" t="inlineStr">
         <is>
           <t>මට PDF file එක 25MBට වඩා ලොකු නිසා upload වෙන්නේ නෑනේ ඉතින් link එකක් විදිහට GoogleDrive එකේ ශරීකරන්න හිතන් ඉන්නේ. ඔයාට පුලුවන්නම් file name එක IT3040_Assignment1_Final.pdf කියලා රේණමේකරලා permission anyone-with-link වලට setකරන්න. නැත්නම් lecturer open කරද්දි access issue එනවා please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="F154" s="7" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2718,22 +2718,22 @@
       <c r="F157" s="4" t="n"/>
     </row>
     <row r="158" ht="49.95" customHeight="1">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" s="5" t="inlineStr">
         <is>
           <t>Neg_0040</t>
         </is>
       </c>
-      <c r="B158" s="7" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C158" s="5" t="inlineStr">
+      <c r="C158" s="6" t="inlineStr">
         <is>
           <t>tharindu aiye oyata puluwannam meeting ekata passe 10min withara onlineinna mage login issue eka balaganna. mama password reset kala eth OTP eka mobile ekata enne ne. email eke spam folder ekath checkkala. heta 8AMta kalin meka fix wenna one nisa poddak help ekak denna puluwanda please meka ikmanata balanna</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
+      <c r="D158" s="7" t="inlineStr">
         <is>
           <t>Tharindu අයියේ ඔයාට පුළුවන්නම් meeting එකට පස්සේ 10min විතර online ඉන්න මගේ login issue එක බලගන්න. මම password reset කළා එත් OTP එක mobile එකට එන්නේ නෑ. email එකේ spam folder එකත් check කළා. හෙට 8AMට කලින් මේක fix වෙන්න ඕන නිසා පොඩ්ඩක් help එකක් දෙන්න පුළුවන්ද please මේක ඉක්මනට බලන්න</t>
         </is>
@@ -2743,7 +2743,7 @@
           <t>තරිඳු අයියේ ඔයාට පුලුවන්නම් meeting එකට පස්සේ 10min විතර onlineඉන්න මගේ login issue එක බලාගන්න. මම password reset කළා ඒත් OTP ඒක mobile එකට එන්නේ නෑ. email එකේ spam folder එකත් check කළා. හෙට 8AMට කලින් මේක fix වෙන්න ඕනේ නිසා පොඩ්ඩක් help එකක් දෙන්න පුලුවන්ද please මේක ඉක්මනට බලන්න</t>
         </is>
       </c>
-      <c r="F158" s="7" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2774,32 +2774,32 @@
       <c r="F161" s="4" t="n"/>
     </row>
     <row r="162" ht="49.95" customHeight="1">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>Neg_0041</t>
         </is>
       </c>
-      <c r="B162" s="7" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C162" s="5" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
         <is>
           <t>mama ada canteen eke QRpayment karaddi Rs350k kapuna eth receipt eka email ekata awe nane eka kohomada check karanne? cashier kiwwa transaction ID eka app eke thiyenawa kiyala. oyata puluwannam app settings walin history eka openkarala screenshot ekak ewanna, nathnam refund request danna bari wenawa</t>
         </is>
       </c>
-      <c r="D162" s="6" t="inlineStr">
+      <c r="D162" s="7" t="inlineStr">
         <is>
           <t>මම අද canteen එකේ QR payment කරද්දී Rs.350ක් කැපුණා එත් receipt එක email එකට ආවේ නෑනේ ඒක කොහොමද check කරන්නේ? cashier කිව්වා transaction ID එක app එකේ තියෙනවා කියලා. ඔයාට පුළුවන්නම් app settings වලින් history එක open කරලා screenshot එකක් එවන්න, නැත්නම් refund request දාන්න බැරි වෙනවා</t>
         </is>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="7" t="inlineStr">
         <is>
           <t>මම අද canteen එකේ QRpayment කරද්දි Rs350ක් කපුනා ඒත් receipt එක email එකට ආවේ නෑනේ ඒක කොහොමද check කරන්නේ? cashier කිව්වා transaction ID ඒක app එකේ තියෙනවා කියලා. ඔයාට පුලුවන්නම් app settings වලින් history එක open කරලා screenshot එකක් එවන්න, නැත්නම් refund request දාන්න බැරි වෙනවා</t>
         </is>
       </c>
-      <c r="F162" s="7" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2830,32 +2830,32 @@
       <c r="F165" s="4" t="n"/>
     </row>
     <row r="166" ht="49.95" customHeight="1">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>Neg_0042</t>
         </is>
       </c>
-      <c r="B166" s="7" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C166" s="5" t="inlineStr">
-        <is>
-          <t>mevideo eka 1080pwalin playwenne nadda?</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
-        <is>
-          <t>මේ video එක 1080p වලින් play වෙන්නේ නැද්ද?</t>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>ayubowanobata suba dawasak wewa🙂</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>ආයුබෝවන් ඔබට සුබ දවසක් වේවා 🙂</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>මේ video එක 1080pවලින් playවෙන්නේ නැද්ද?</t>
-        </is>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
+          <t>ආයුබෝවනොබට සුබ දවසක් වේවා🙂</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2886,32 +2886,32 @@
       <c r="F169" s="4" t="n"/>
     </row>
     <row r="170" ht="49.95" customHeight="1">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>Neg_0043</t>
         </is>
       </c>
-      <c r="B170" s="7" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C170" s="5" t="inlineStr">
-        <is>
-          <t>mtaassignment1ka submitkrnna one heta</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>මට assignment එක submit කරන්න ඕන හෙට</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>මටassignment එක submit කරන්න ඕනේ හෙට</t>
-        </is>
-      </c>
-      <c r="F170" s="7" t="inlineStr">
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>subaudasanak wewa machn oyath enawada?</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>සුබ උදෑසනක් වේවා මචං ඔයත් එනවද?</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>සුබඋදාසනක් වේවා මචන් ඔයත් එනවද?</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2942,32 +2942,32 @@
       <c r="F173" s="4" t="n"/>
     </row>
     <row r="174" ht="49.95" customHeight="1">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>Neg_0044</t>
         </is>
       </c>
-      <c r="B174" s="7" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C174" s="5" t="inlineStr">
-        <is>
-          <t>mnmySQLbackup eka 2GB wage haduwa</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>මං MySQL backup එක 2GB වගේ හැදුවා</t>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>harihari mneka 6.30PMkarannam bn</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>හරි හරි මං ඒක 6.30PM කරන්නම් බන්</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>මන්mySQLbackup එක 2GB වගේ හැදුවා</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr">
+          <t>හරිහරි මන්එක 6.30PM කරන්නම් බන්</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -2998,32 +2998,32 @@
       <c r="F177" s="4" t="n"/>
     </row>
     <row r="178" ht="49.95" customHeight="1">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>Neg_0045</t>
         </is>
       </c>
-      <c r="B178" s="7" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C178" s="5" t="inlineStr">
-        <is>
-          <t>apiNegombo beachside cafe ekata yanawada?</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>අපි Negombo beachside cafe එකට යනවද?</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>අපි නැගැම්බෝ beachside cafe එකට යනවද?</t>
-        </is>
-      </c>
-      <c r="F178" s="7" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>anehari aiye mata okkoma theruna</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>අනේ හරි අයියේ මට ඔක්කොම තේරුණා</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>අනේහරි අයියෙ මට ඔක්කොම තේරුනා</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3054,32 +3054,32 @@
       <c r="F181" s="4" t="n"/>
     </row>
     <row r="182" ht="49.95" customHeight="1">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" s="5" t="inlineStr">
         <is>
           <t>Neg_0046</t>
         </is>
       </c>
-      <c r="B182" s="7" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C182" s="5" t="inlineStr">
-        <is>
-          <t>oytExcelrow eka deletewela nadda balanna</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>ඔයාට Excel row එක delete වෙලා නැද්ද බලන්න</t>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>chuttachutta uploadkrnna trykrnn</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>චුට්ට චුට්ට upload කරන්න try කරන්න</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>ඔයාට Excelrow එක deleteවෙලා නැද්ද බලන්න</t>
-        </is>
-      </c>
-      <c r="F182" s="7" t="inlineStr">
+          <t>චුට්ටචුට්ටා උඩුඩ්කරන්න ට්රැක්රන්න</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3110,32 +3110,32 @@
       <c r="F185" s="4" t="n"/>
     </row>
     <row r="186" ht="49.95" customHeight="1">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
         <is>
           <t>Neg_0047</t>
         </is>
       </c>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C186" s="5" t="inlineStr">
-        <is>
-          <t>adofile eka downloadwenne nane serverdown da?</t>
-        </is>
-      </c>
-      <c r="D186" s="6" t="inlineStr">
-        <is>
-          <t>අඩෝ file එක download වෙන්නේ නෑනේ server down ද?</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="inlineStr">
-        <is>
-          <t>අඩොෆිල් එක download වෙන්නේ නෑනේ සර්වර්ඩවුන් ද?</t>
-        </is>
-      </c>
-      <c r="F186" s="7" t="inlineStr">
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>ikmanikmanata link eka ewnna plz</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>ඉක්මන් ඉක්මනට link එක එවන්න please</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>ඉක්මනික්මනට link එක එවන්න please</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3166,32 +3166,32 @@
       <c r="F189" s="4" t="n"/>
     </row>
     <row r="190" ht="49.95" customHeight="1">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="5" t="inlineStr">
         <is>
           <t>Neg_0048</t>
         </is>
       </c>
-      <c r="B190" s="7" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="C190" s="5" t="inlineStr">
-        <is>
-          <t>oytaheta 8.15AMta Teamslink eka ewnna puluwnd bn</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
-        <is>
-          <t>ඔයාට හෙට 8.15AMට Teams link එක එවන්න පුළුවන්ද බන්</t>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>mn3kmwithara payin giya bn</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>මං 3km විතර පයින් ගියා බන්</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>ඔයාට හෙට 8.15AMට Teamslink එක එවන්න පුළුවන්ද බං</t>
-        </is>
-      </c>
-      <c r="F190" s="7" t="inlineStr">
+          <t>මන් 3kmවිතර පයින් ගියා බන්</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3222,32 +3222,32 @@
       <c r="F193" s="4" t="n"/>
     </row>
     <row r="194" ht="49.95" customHeight="1">
-      <c r="A194" s="2" t="inlineStr">
+      <c r="A194" s="5" t="inlineStr">
         <is>
           <t>Neg_0049</t>
         </is>
       </c>
-      <c r="B194" s="7" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C194" s="5" t="inlineStr">
-        <is>
-          <t>oyagephone number eka +94771234567 da?</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
-        <is>
-          <t>ඔයාගේ phone number එක +94771234567 ද?</t>
-        </is>
-      </c>
-      <c r="E194" s="6" t="inlineStr">
-        <is>
-          <t>ඔයාගේෆොනේ number එක +94771234567 ද?</t>
-        </is>
-      </c>
-      <c r="F194" s="7" t="inlineStr">
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>me table eka adi6kwithara usaida?</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>මේ table එක අඩි 6ක් විතර උසයිද?</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>මේ table එක අඩි 6ක්විතර උසයිද?</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3278,22 +3278,22 @@
       <c r="F197" s="4" t="n"/>
     </row>
     <row r="198" ht="49.95" customHeight="1">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="A198" s="5" t="inlineStr">
         <is>
           <t>Neg_0050</t>
         </is>
       </c>
-      <c r="B198" s="7" t="inlineStr">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C198" s="5" t="inlineStr">
+      <c r="C198" s="6" t="inlineStr">
         <is>
           <t>ubadata eka backupkrla external drive ekata danna</t>
         </is>
       </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="D198" s="7" t="inlineStr">
         <is>
           <t>උඹ data එක backup කරලා external drive එකට දාන්න</t>
         </is>
@@ -3303,7 +3303,7 @@
           <t>උබදට ඒක backup කරලා external drive එකට දාන්න</t>
         </is>
       </c>
-      <c r="F198" s="7" t="inlineStr">
+      <c r="F198" s="2" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -3337,19 +3337,19 @@
   <mergeCells count="300">
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C154:C157"/>
     <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C154:C157"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="A166:A169"/>
     <mergeCell ref="E102:E105"/>
     <mergeCell ref="B50:B53"/>
     <mergeCell ref="A162:A165"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="C30:C33"/>
     <mergeCell ref="C162:C165"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="F30:F33"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="D46:D49"/>
     <mergeCell ref="C54:C57"/>
@@ -3359,168 +3359,168 @@
     <mergeCell ref="F198:F201"/>
     <mergeCell ref="C146:C149"/>
     <mergeCell ref="D174:D177"/>
+    <mergeCell ref="F174:F177"/>
     <mergeCell ref="A178:A181"/>
-    <mergeCell ref="F174:F177"/>
+    <mergeCell ref="C94:C97"/>
     <mergeCell ref="D126:D129"/>
-    <mergeCell ref="C94:C97"/>
     <mergeCell ref="A74:A77"/>
+    <mergeCell ref="E94:E97"/>
     <mergeCell ref="F126:F129"/>
     <mergeCell ref="D166:D169"/>
-    <mergeCell ref="E94:E97"/>
     <mergeCell ref="E90:E93"/>
+    <mergeCell ref="B38:B41"/>
     <mergeCell ref="F110:F113"/>
     <mergeCell ref="D150:D153"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="A98:A101"/>
     <mergeCell ref="F150:F153"/>
     <mergeCell ref="E158:E161"/>
     <mergeCell ref="A18:A21"/>
     <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E74:E77"/>
     <mergeCell ref="B166:B169"/>
-    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="F42:F45"/>
     <mergeCell ref="B78:B81"/>
-    <mergeCell ref="F42:F45"/>
     <mergeCell ref="B118:B121"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B158:B161"/>
     <mergeCell ref="E154:E157"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="A2:A5"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="E2:E5"/>
+    <mergeCell ref="C82:C85"/>
     <mergeCell ref="B186:B189"/>
-    <mergeCell ref="C82:C85"/>
     <mergeCell ref="D102:D105"/>
     <mergeCell ref="B142:B145"/>
+    <mergeCell ref="D142:D145"/>
     <mergeCell ref="E174:E177"/>
-    <mergeCell ref="D142:D145"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="A150:A153"/>
     <mergeCell ref="E26:E29"/>
+    <mergeCell ref="C66:C69"/>
     <mergeCell ref="D98:D101"/>
-    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="E66:E69"/>
     <mergeCell ref="F98:F101"/>
     <mergeCell ref="A102:A105"/>
-    <mergeCell ref="E66:E69"/>
     <mergeCell ref="C102:C105"/>
+    <mergeCell ref="B26:B29"/>
     <mergeCell ref="A34:A37"/>
-    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="C34:C37"/>
     <mergeCell ref="E50:E53"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C34:C37"/>
     <mergeCell ref="C86:C89"/>
     <mergeCell ref="F82:F85"/>
-    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="D54:D57"/>
     <mergeCell ref="E130:E133"/>
-    <mergeCell ref="D54:D57"/>
     <mergeCell ref="B134:B137"/>
     <mergeCell ref="B194:B197"/>
     <mergeCell ref="D10:D13"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="D50:D53"/>
     <mergeCell ref="B90:B93"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="F10:F13"/>
     <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B122:B125"/>
     <mergeCell ref="F146:F149"/>
-    <mergeCell ref="B122:B125"/>
     <mergeCell ref="E150:E153"/>
     <mergeCell ref="D178:D181"/>
     <mergeCell ref="D34:D37"/>
     <mergeCell ref="F178:F181"/>
-    <mergeCell ref="A182:A185"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="F34:F37"/>
     <mergeCell ref="C42:C45"/>
-    <mergeCell ref="F34:F37"/>
+    <mergeCell ref="E42:E45"/>
     <mergeCell ref="F74:F77"/>
     <mergeCell ref="A78:A81"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="A182:A185"/>
     <mergeCell ref="B106:B109"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="C22:C25"/>
+    <mergeCell ref="F18:F21"/>
     <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="E78:E81"/>
     <mergeCell ref="B170:B173"/>
-    <mergeCell ref="E78:E81"/>
     <mergeCell ref="A174:A177"/>
     <mergeCell ref="D170:D173"/>
+    <mergeCell ref="F2:F5"/>
     <mergeCell ref="B58:B61"/>
-    <mergeCell ref="F2:F5"/>
     <mergeCell ref="E6:E9"/>
     <mergeCell ref="C134:C137"/>
     <mergeCell ref="E186:E189"/>
+    <mergeCell ref="F22:F25"/>
     <mergeCell ref="C114:C117"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="E114:E117"/>
     <mergeCell ref="A154:A157"/>
-    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="E170:E173"/>
     <mergeCell ref="A194:A197"/>
-    <mergeCell ref="E170:E173"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="C46:C49"/>
     <mergeCell ref="F190:F193"/>
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="C138:C141"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E54:E57"/>
     <mergeCell ref="C178:C181"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
     <mergeCell ref="E178:E181"/>
     <mergeCell ref="D62:D65"/>
     <mergeCell ref="D118:D121"/>
     <mergeCell ref="F62:F65"/>
     <mergeCell ref="B198:B201"/>
+    <mergeCell ref="D14:D17"/>
     <mergeCell ref="A106:A109"/>
-    <mergeCell ref="D14:D17"/>
     <mergeCell ref="F14:F17"/>
     <mergeCell ref="B174:B177"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="B126:B129"/>
     <mergeCell ref="D182:D185"/>
+    <mergeCell ref="D38:D41"/>
     <mergeCell ref="A130:A133"/>
     <mergeCell ref="F182:F185"/>
-    <mergeCell ref="D38:D41"/>
     <mergeCell ref="A82:A85"/>
     <mergeCell ref="B110:B113"/>
     <mergeCell ref="E106:E109"/>
+    <mergeCell ref="B54:B57"/>
     <mergeCell ref="D110:D113"/>
-    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="A58:A61"/>
     <mergeCell ref="E146:E149"/>
-    <mergeCell ref="A58:A61"/>
     <mergeCell ref="F166:F169"/>
     <mergeCell ref="E198:E201"/>
     <mergeCell ref="C74:C77"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="A110:A113"/>
     <mergeCell ref="C126:C129"/>
+    <mergeCell ref="E126:E129"/>
     <mergeCell ref="F162:F165"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="E126:E129"/>
     <mergeCell ref="C166:C169"/>
-    <mergeCell ref="B94:B97"/>
     <mergeCell ref="C58:C61"/>
     <mergeCell ref="E58:E61"/>
     <mergeCell ref="D90:D93"/>
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="B102:B105"/>
     <mergeCell ref="E138:E141"/>
+    <mergeCell ref="D158:D161"/>
     <mergeCell ref="E190:E193"/>
-    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="A66:A69"/>
     <mergeCell ref="B98:B101"/>
-    <mergeCell ref="A66:A69"/>
     <mergeCell ref="F114:F117"/>
+    <mergeCell ref="A118:A121"/>
     <mergeCell ref="D154:D157"/>
-    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="F26:F29"/>
     <mergeCell ref="C118:C121"/>
     <mergeCell ref="F154:F157"/>
     <mergeCell ref="A158:A161"/>
-    <mergeCell ref="F26:F29"/>
     <mergeCell ref="D186:D189"/>
+    <mergeCell ref="A6:A9"/>
     <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A6:A9"/>
     <mergeCell ref="C50:C53"/>
     <mergeCell ref="B82:B85"/>
     <mergeCell ref="A86:A89"/>
@@ -3530,28 +3530,27 @@
     <mergeCell ref="E118:E121"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="E46:E49"/>
-    <mergeCell ref="C158:C161"/>
     <mergeCell ref="D66:D69"/>
     <mergeCell ref="D106:D109"/>
+    <mergeCell ref="F66:F69"/>
     <mergeCell ref="B146:B149"/>
-    <mergeCell ref="F66:F69"/>
     <mergeCell ref="D18:D21"/>
     <mergeCell ref="D146:D149"/>
     <mergeCell ref="E166:E169"/>
     <mergeCell ref="A26:A29"/>
+    <mergeCell ref="E86:E89"/>
     <mergeCell ref="B178:B181"/>
-    <mergeCell ref="E86:E89"/>
     <mergeCell ref="B34:B37"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="F50:F53"/>
     <mergeCell ref="B74:B77"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="E162:E165"/>
     <mergeCell ref="D130:D133"/>
     <mergeCell ref="A14:A17"/>
+    <mergeCell ref="E162:E165"/>
     <mergeCell ref="F130:F133"/>
+    <mergeCell ref="A134:A137"/>
     <mergeCell ref="B162:B165"/>
-    <mergeCell ref="A134:A137"/>
     <mergeCell ref="C194:C197"/>
     <mergeCell ref="C38:C41"/>
     <mergeCell ref="D58:D61"/>
@@ -3567,26 +3566,26 @@
     <mergeCell ref="E142:E145"/>
     <mergeCell ref="C18:C21"/>
     <mergeCell ref="E194:E197"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="E18:E21"/>
     <mergeCell ref="B150:B153"/>
-    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="D22:D25"/>
     <mergeCell ref="A114:A117"/>
     <mergeCell ref="A170:A173"/>
-    <mergeCell ref="D22:D25"/>
     <mergeCell ref="A70:A73"/>
+    <mergeCell ref="F78:F81"/>
     <mergeCell ref="C170:C173"/>
-    <mergeCell ref="F78:F81"/>
     <mergeCell ref="F118:F121"/>
-    <mergeCell ref="E18:E21"/>
     <mergeCell ref="F158:F161"/>
     <mergeCell ref="B190:B193"/>
+    <mergeCell ref="D6:D9"/>
     <mergeCell ref="C26:C29"/>
-    <mergeCell ref="D6:D9"/>
     <mergeCell ref="D190:D193"/>
+    <mergeCell ref="F6:F9"/>
     <mergeCell ref="B86:B89"/>
-    <mergeCell ref="A138:A141"/>
     <mergeCell ref="E82:E85"/>
     <mergeCell ref="D86:D89"/>
-    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="A138:A141"/>
     <mergeCell ref="F86:F89"/>
     <mergeCell ref="F142:F145"/>
     <mergeCell ref="C10:C13"/>
@@ -3602,26 +3601,28 @@
     <mergeCell ref="D134:D137"/>
     <mergeCell ref="D194:D197"/>
     <mergeCell ref="F134:F137"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="F194:F197"/>
     <mergeCell ref="A198:A201"/>
-    <mergeCell ref="F194:F197"/>
     <mergeCell ref="C198:C201"/>
+    <mergeCell ref="C90:C93"/>
     <mergeCell ref="D122:D125"/>
-    <mergeCell ref="C90:C93"/>
     <mergeCell ref="F122:F125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="C130:C133"/>
     <mergeCell ref="D162:D165"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="A126:A129"/>
     <mergeCell ref="C182:C185"/>
+    <mergeCell ref="A142:A145"/>
     <mergeCell ref="E182:E185"/>
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="F106:F109"/>
     <mergeCell ref="F186:F189"/>
+    <mergeCell ref="C150:C153"/>
     <mergeCell ref="A190:A193"/>
-    <mergeCell ref="C150:C153"/>
     <mergeCell ref="C190:C193"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="D74:D77"/>
     <mergeCell ref="B114:B117"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="E22:E25"/>
     <mergeCell ref="D114:D117"/>
     <mergeCell ref="B154:B157"/>
     <mergeCell ref="C174:C177"/>
@@ -3629,12 +3630,11 @@
     <mergeCell ref="B138:B141"/>
     <mergeCell ref="E134:E137"/>
     <mergeCell ref="D138:D141"/>
-    <mergeCell ref="F22:F25"/>
     <mergeCell ref="F54:F57"/>
-    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="C158:C161"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="C62:C65"/>
-    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="A98:A101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
